--- a/calendar_chilean_2022A.xlsx
+++ b/calendar_chilean_2022A.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ed268546/Dropbox/Mac/Documents/codes/SPOCK_chilean/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4567032-4966-6644-9580-DD5A0B1837C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE8750E-47A7-AA44-AA0B-8A4435DD5B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{29A8BF1E-0110-C24B-9407-C010B9269ACA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21100" xr2:uid="{29A8BF1E-0110-C24B-9407-C010B9269ACA}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="47">
   <si>
     <t>Date</t>
   </si>
@@ -174,6 +173,9 @@
   </si>
   <si>
     <t>Program ID</t>
+  </si>
+  <si>
+    <t>technical but caught up</t>
   </si>
 </sst>
 </file>
@@ -676,7 +678,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -836,15 +838,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1172,7 +1168,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="10.83203125" style="14"/>
-    <col min="7" max="7" width="15.33203125" style="63" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
     <col min="8" max="8" width="10.83203125" style="14"/>
     <col min="9" max="9" width="51.33203125" style="14" customWidth="1"/>
     <col min="10" max="10" width="19" customWidth="1"/>
@@ -1180,7 +1176,7 @@
     <col min="13" max="13" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1199,7 +1195,7 @@
       <c r="F1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="66" t="s">
+      <c r="G1" s="62" t="s">
         <v>45</v>
       </c>
       <c r="H1" s="18" t="s">
@@ -1212,7 +1208,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" s="25">
         <v>44652</v>
       </c>
@@ -1231,7 +1227,7 @@
       <c r="F2" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="64" t="s">
+      <c r="G2" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H2" s="39" t="s">
@@ -1244,7 +1240,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="26">
         <v>44653</v>
       </c>
@@ -1263,7 +1259,7 @@
       <c r="F3" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H3" s="16" t="s">
@@ -1276,7 +1272,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="26">
         <v>44654</v>
       </c>
@@ -1295,7 +1291,7 @@
       <c r="F4" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H4" s="16" t="s">
@@ -1308,7 +1304,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="26">
         <v>44655</v>
       </c>
@@ -1325,10 +1321,9 @@
         <v>0</v>
       </c>
       <c r="F5" s="13"/>
-      <c r="G5" s="61"/>
       <c r="J5" s="10"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="26">
         <v>44656</v>
       </c>
@@ -1345,10 +1340,9 @@
         <v>0</v>
       </c>
       <c r="F6" s="13"/>
-      <c r="G6" s="61"/>
       <c r="J6" s="10"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="26">
         <v>44657</v>
       </c>
@@ -1365,10 +1359,9 @@
         <v>0</v>
       </c>
       <c r="F7" s="13"/>
-      <c r="G7" s="61"/>
       <c r="J7" s="10"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="26">
         <v>44658</v>
       </c>
@@ -1385,10 +1378,9 @@
         <v>0</v>
       </c>
       <c r="F8" s="13"/>
-      <c r="G8" s="61"/>
       <c r="J8" s="10"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="26">
         <v>44659</v>
       </c>
@@ -1405,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="F9" s="13"/>
-      <c r="G9" s="59"/>
+      <c r="G9" s="14"/>
       <c r="J9" s="10"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="26">
         <v>44660</v>
       </c>
@@ -1425,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="13"/>
-      <c r="G10" s="59"/>
+      <c r="G10" s="14"/>
       <c r="J10" s="10"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="26">
         <v>44661</v>
       </c>
@@ -1447,7 +1439,7 @@
       <c r="F11" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="60" t="s">
+      <c r="G11" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H11" s="16" t="s">
@@ -1460,7 +1452,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="26">
         <v>44662</v>
       </c>
@@ -1479,7 +1471,7 @@
       <c r="F12" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="60" t="s">
+      <c r="G12" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H12" s="16" t="s">
@@ -1491,8 +1483,11 @@
       <c r="J12" s="45" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="26">
         <v>44663</v>
       </c>
@@ -1511,7 +1506,7 @@
       <c r="F13" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="65" t="s">
+      <c r="G13" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H13" s="16" t="s">
@@ -1524,7 +1519,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="26">
         <v>44664</v>
       </c>
@@ -1543,7 +1538,7 @@
       <c r="F14" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G14" s="60" t="s">
+      <c r="G14" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H14" s="16" t="s">
@@ -1556,7 +1551,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="26">
         <v>44665</v>
       </c>
@@ -1573,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="F15" s="13"/>
-      <c r="G15" s="59"/>
+      <c r="G15" s="14"/>
       <c r="J15" s="10"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A16" s="26">
         <v>44666</v>
       </c>
@@ -1593,7 +1588,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="13"/>
-      <c r="G16" s="59"/>
+      <c r="G16" s="14"/>
       <c r="J16" s="10"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
@@ -1613,7 +1608,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="13"/>
-      <c r="G17" s="59"/>
+      <c r="G17" s="14"/>
       <c r="J17" s="10"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
@@ -1633,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="13"/>
-      <c r="G18" s="59"/>
+      <c r="G18" s="14"/>
       <c r="J18" s="10"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
@@ -1653,7 +1648,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="13"/>
-      <c r="G19" s="59"/>
+      <c r="G19" s="14"/>
       <c r="J19" s="10"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
@@ -1675,7 +1670,7 @@
       <c r="F20" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G20" s="60" t="s">
+      <c r="G20" s="59" t="s">
         <v>42</v>
       </c>
       <c r="H20" s="16" t="s">
@@ -1707,7 +1702,7 @@
       <c r="F21" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G21" s="60" t="s">
+      <c r="G21" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H21" s="16" t="s">
@@ -1739,7 +1734,7 @@
       <c r="F22" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G22" s="60" t="s">
+      <c r="G22" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H22" s="16" t="s">
@@ -1769,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="13"/>
-      <c r="G23" s="59"/>
+      <c r="G23" s="14"/>
       <c r="J23" s="10"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
@@ -1789,7 +1784,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="13"/>
-      <c r="G24" s="59"/>
+      <c r="G24" s="14"/>
       <c r="J24" s="10"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
@@ -1809,7 +1804,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="13"/>
-      <c r="G25" s="59"/>
+      <c r="G25" s="14"/>
       <c r="J25" s="10"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
@@ -1829,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="13"/>
-      <c r="G26" s="59"/>
+      <c r="G26" s="14"/>
       <c r="J26" s="10"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
@@ -1849,7 +1844,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="13"/>
-      <c r="G27" s="59"/>
+      <c r="G27" s="14"/>
       <c r="J27" s="10"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
@@ -1869,7 +1864,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="13"/>
-      <c r="G28" s="59"/>
+      <c r="G28" s="14"/>
       <c r="J28" s="10"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
@@ -1891,7 +1886,7 @@
       <c r="F29" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="64" t="s">
+      <c r="G29" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H29" s="16" t="s">
@@ -1923,7 +1918,7 @@
       <c r="F30" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G30" s="64" t="s">
+      <c r="G30" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H30" s="16" t="s">
@@ -1955,7 +1950,7 @@
       <c r="F31" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G31" s="64" t="s">
+      <c r="G31" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H31" s="16" t="s">
@@ -1985,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="13"/>
-      <c r="G32" s="59"/>
+      <c r="G32" s="14"/>
       <c r="J32" s="10"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
@@ -2005,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="13"/>
-      <c r="G33" s="59"/>
+      <c r="G33" s="14"/>
       <c r="J33" s="10"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
@@ -2025,7 +2020,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="13"/>
-      <c r="G34" s="59"/>
+      <c r="G34" s="14"/>
       <c r="J34" s="10"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.2">
@@ -2045,7 +2040,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="13"/>
-      <c r="G35" s="59"/>
+      <c r="G35" s="14"/>
       <c r="J35" s="10"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.2">
@@ -2065,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="13"/>
-      <c r="G36" s="59"/>
+      <c r="G36" s="14"/>
       <c r="J36" s="10"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
@@ -2085,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="13"/>
-      <c r="G37" s="59"/>
+      <c r="G37" s="14"/>
       <c r="J37" s="10"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.2">
@@ -2107,7 +2102,7 @@
       <c r="F38" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G38" s="60" t="s">
+      <c r="G38" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H38" s="16" t="s">
@@ -2139,7 +2134,7 @@
       <c r="F39" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G39" s="60" t="s">
+      <c r="G39" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H39" s="16" t="s">
@@ -2171,7 +2166,7 @@
       <c r="F40" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G40" s="60" t="s">
+      <c r="G40" s="59" t="s">
         <v>41</v>
       </c>
       <c r="H40" s="16" t="s">
@@ -2201,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="13"/>
-      <c r="G41" s="59"/>
+      <c r="G41" s="14"/>
       <c r="J41" s="10"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.2">
@@ -2221,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="13"/>
-      <c r="G42" s="59"/>
+      <c r="G42" s="14"/>
       <c r="J42" s="10"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.2">
@@ -2241,7 +2236,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="13"/>
-      <c r="G43" s="59"/>
+      <c r="G43" s="14"/>
       <c r="J43" s="10"/>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.2">
@@ -2261,7 +2256,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="13"/>
-      <c r="G44" s="59"/>
+      <c r="G44" s="14"/>
       <c r="J44" s="10"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
@@ -2281,7 +2276,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="13"/>
-      <c r="G45" s="59"/>
+      <c r="G45" s="14"/>
       <c r="J45" s="10"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.2">
@@ -2301,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="13"/>
-      <c r="G46" s="59"/>
+      <c r="G46" s="14"/>
       <c r="J46" s="10"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.2">
@@ -2323,7 +2318,7 @@
       <c r="F47" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G47" s="65" t="s">
+      <c r="G47" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H47" s="16" t="s">
@@ -2355,7 +2350,7 @@
       <c r="F48" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G48" s="65" t="s">
+      <c r="G48" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H48" s="16" t="s">
@@ -2387,7 +2382,7 @@
       <c r="F49" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G49" s="60" t="s">
+      <c r="G49" s="59" t="s">
         <v>41</v>
       </c>
       <c r="H49" s="16" t="s">
@@ -2417,7 +2412,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="13"/>
-      <c r="G50" s="59"/>
+      <c r="G50" s="14"/>
       <c r="J50" s="10"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.2">
@@ -2437,7 +2432,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="13"/>
-      <c r="G51" s="59"/>
+      <c r="G51" s="14"/>
       <c r="J51" s="10"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.2">
@@ -2457,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="13"/>
-      <c r="G52" s="59"/>
+      <c r="G52" s="14"/>
       <c r="J52" s="10"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.2">
@@ -2477,7 +2472,6 @@
         <v>0</v>
       </c>
       <c r="F53" s="13"/>
-      <c r="G53" s="61"/>
       <c r="J53" s="10"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.2">
@@ -2497,7 +2491,6 @@
         <v>0</v>
       </c>
       <c r="F54" s="13"/>
-      <c r="G54" s="61"/>
       <c r="J54" s="10"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.2">
@@ -2517,7 +2510,6 @@
         <v>0</v>
       </c>
       <c r="F55" s="13"/>
-      <c r="G55" s="61"/>
       <c r="J55" s="10"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.2">
@@ -2539,7 +2531,7 @@
       <c r="F56" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G56" s="64" t="s">
+      <c r="G56" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H56" s="16" t="s">
@@ -2571,7 +2563,7 @@
       <c r="F57" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G57" s="64" t="s">
+      <c r="G57" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H57" s="16" t="s">
@@ -2603,7 +2595,7 @@
       <c r="F58" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="64" t="s">
+      <c r="G58" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H58" s="16" t="s">
@@ -2633,7 +2625,6 @@
         <v>0</v>
       </c>
       <c r="F59" s="13"/>
-      <c r="G59" s="61"/>
       <c r="J59" s="10"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.2">
@@ -2653,7 +2644,6 @@
         <v>0</v>
       </c>
       <c r="F60" s="13"/>
-      <c r="G60" s="61"/>
       <c r="J60" s="10"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.2">
@@ -2673,7 +2663,6 @@
         <v>0</v>
       </c>
       <c r="F61" s="13"/>
-      <c r="G61" s="61"/>
       <c r="J61" s="10"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.2">
@@ -2693,7 +2682,6 @@
         <v>0</v>
       </c>
       <c r="F62" s="13"/>
-      <c r="G62" s="61"/>
       <c r="J62" s="10"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.2">
@@ -2713,7 +2701,6 @@
         <v>0</v>
       </c>
       <c r="F63" s="13"/>
-      <c r="G63" s="61"/>
       <c r="J63" s="10"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.2">
@@ -2733,7 +2720,6 @@
         <v>0</v>
       </c>
       <c r="F64" s="13"/>
-      <c r="G64" s="61"/>
       <c r="J64" s="10"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.2">
@@ -2755,7 +2741,7 @@
       <c r="F65" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G65" s="64" t="s">
+      <c r="G65" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H65" s="16" t="s">
@@ -2787,7 +2773,7 @@
       <c r="F66" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G66" s="64" t="s">
+      <c r="G66" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H66" s="16" t="s">
@@ -2819,7 +2805,7 @@
       <c r="F67" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G67" s="64" t="s">
+      <c r="G67" s="60" t="s">
         <v>44</v>
       </c>
       <c r="H67" s="16" t="s">
@@ -2849,7 +2835,6 @@
         <v>0</v>
       </c>
       <c r="F68" s="13"/>
-      <c r="G68" s="61"/>
       <c r="J68" s="10"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
@@ -2869,7 +2854,6 @@
         <v>0</v>
       </c>
       <c r="F69" s="13"/>
-      <c r="G69" s="61"/>
       <c r="J69" s="10"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.2">
@@ -2889,7 +2873,6 @@
         <v>0</v>
       </c>
       <c r="F70" s="13"/>
-      <c r="G70" s="61"/>
       <c r="J70" s="10"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.2">
@@ -2909,7 +2892,6 @@
         <v>0</v>
       </c>
       <c r="F71" s="13"/>
-      <c r="G71" s="61"/>
       <c r="J71" s="10"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.2">
@@ -2929,7 +2911,6 @@
         <v>0</v>
       </c>
       <c r="F72" s="13"/>
-      <c r="G72" s="61"/>
       <c r="J72" s="10"/>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.2">
@@ -2949,7 +2930,6 @@
         <v>0</v>
       </c>
       <c r="F73" s="13"/>
-      <c r="G73" s="61"/>
       <c r="J73" s="10"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.2">
@@ -2971,7 +2951,7 @@
       <c r="F74" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G74" s="65" t="s">
+      <c r="G74" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H74" s="16" t="s">
@@ -3003,7 +2983,7 @@
       <c r="F75" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G75" s="65" t="s">
+      <c r="G75" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H75" s="16" t="s">
@@ -3035,7 +3015,7 @@
       <c r="F76" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G76" s="65" t="s">
+      <c r="G76" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H76" s="16" t="s">
@@ -3065,7 +3045,6 @@
         <v>0</v>
       </c>
       <c r="F77" s="13"/>
-      <c r="G77" s="61"/>
       <c r="J77" s="10"/>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.2">
@@ -3085,7 +3064,6 @@
         <v>0</v>
       </c>
       <c r="F78" s="13"/>
-      <c r="G78" s="61"/>
       <c r="J78" s="10"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.2">
@@ -3105,7 +3083,6 @@
         <v>0</v>
       </c>
       <c r="F79" s="13"/>
-      <c r="G79" s="61"/>
       <c r="J79" s="10"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.2">
@@ -3125,7 +3102,6 @@
         <v>0</v>
       </c>
       <c r="F80" s="13"/>
-      <c r="G80" s="61"/>
       <c r="J80" s="10"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.2">
@@ -3145,7 +3121,6 @@
         <v>0</v>
       </c>
       <c r="F81" s="13"/>
-      <c r="G81" s="61"/>
       <c r="J81" s="10"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.2">
@@ -3165,7 +3140,6 @@
         <v>0</v>
       </c>
       <c r="F82" s="13"/>
-      <c r="G82" s="61"/>
       <c r="J82" s="10"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.2">
@@ -3187,7 +3161,6 @@
       <c r="F83" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G83" s="61"/>
       <c r="H83" s="16" t="s">
         <v>13</v>
       </c>
@@ -3217,7 +3190,7 @@
       <c r="F84" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G84" s="65" t="s">
+      <c r="G84" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H84" s="16" t="s">
@@ -3249,7 +3222,7 @@
       <c r="F85" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G85" s="65" t="s">
+      <c r="G85" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H85" s="16" t="s">
@@ -3279,7 +3252,6 @@
         <v>0</v>
       </c>
       <c r="F86" s="13"/>
-      <c r="G86" s="61"/>
       <c r="J86" s="10"/>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.2">
@@ -3299,7 +3271,6 @@
         <v>0</v>
       </c>
       <c r="F87" s="13"/>
-      <c r="G87" s="61"/>
       <c r="J87" s="10"/>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.2">
@@ -3319,7 +3290,6 @@
         <v>0</v>
       </c>
       <c r="F88" s="13"/>
-      <c r="G88" s="61"/>
       <c r="J88" s="10"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.2">
@@ -3339,7 +3309,6 @@
         <v>0</v>
       </c>
       <c r="F89" s="13"/>
-      <c r="G89" s="61"/>
       <c r="J89" s="10"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.2">
@@ -3359,7 +3328,6 @@
         <v>0</v>
       </c>
       <c r="F90" s="13"/>
-      <c r="G90" s="61"/>
       <c r="J90" s="10"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.2">
@@ -3379,7 +3347,6 @@
         <v>0</v>
       </c>
       <c r="F91" s="13"/>
-      <c r="G91" s="61"/>
       <c r="J91" s="10"/>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.2">
@@ -3401,7 +3368,7 @@
       <c r="F92" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G92" s="65" t="s">
+      <c r="G92" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H92" s="16" t="s">
@@ -3433,7 +3400,7 @@
       <c r="F93" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G93" s="65" t="s">
+      <c r="G93" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H93" s="16" t="s">
@@ -3465,7 +3432,7 @@
       <c r="F94" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G94" s="65" t="s">
+      <c r="G94" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H94" s="16" t="s">
@@ -3495,7 +3462,6 @@
         <v>0</v>
       </c>
       <c r="F95" s="13"/>
-      <c r="G95" s="61"/>
       <c r="J95" s="10"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.2">
@@ -3515,7 +3481,6 @@
         <v>0</v>
       </c>
       <c r="F96" s="13"/>
-      <c r="G96" s="61"/>
       <c r="J96" s="10"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.2">
@@ -3535,7 +3500,6 @@
         <v>0</v>
       </c>
       <c r="F97" s="13"/>
-      <c r="G97" s="61"/>
       <c r="J97" s="10"/>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.2">
@@ -3555,7 +3519,6 @@
         <v>0</v>
       </c>
       <c r="F98" s="13"/>
-      <c r="G98" s="61"/>
       <c r="J98" s="10"/>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.2">
@@ -3575,7 +3538,6 @@
         <v>0</v>
       </c>
       <c r="F99" s="13"/>
-      <c r="G99" s="61"/>
       <c r="J99" s="10"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.2">
@@ -3595,7 +3557,6 @@
         <v>0</v>
       </c>
       <c r="F100" s="13"/>
-      <c r="G100" s="61"/>
       <c r="J100" s="10"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.2">
@@ -3617,7 +3578,7 @@
       <c r="F101" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G101" s="65" t="s">
+      <c r="G101" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H101" s="16" t="s">
@@ -3649,7 +3610,7 @@
       <c r="F102" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G102" s="65" t="s">
+      <c r="G102" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H102" s="16" t="s">
@@ -3681,7 +3642,7 @@
       <c r="F103" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G103" s="65" t="s">
+      <c r="G103" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H103" s="16" t="s">
@@ -3711,7 +3672,6 @@
         <v>0</v>
       </c>
       <c r="F104" s="13"/>
-      <c r="G104" s="61"/>
       <c r="J104" s="10"/>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.2">
@@ -3731,7 +3691,6 @@
         <v>0</v>
       </c>
       <c r="F105" s="13"/>
-      <c r="G105" s="61"/>
       <c r="J105" s="10"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.2">
@@ -3751,7 +3710,6 @@
         <v>0</v>
       </c>
       <c r="F106" s="13"/>
-      <c r="G106" s="61"/>
       <c r="J106" s="10"/>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.2">
@@ -3771,7 +3729,6 @@
         <v>0</v>
       </c>
       <c r="F107" s="13"/>
-      <c r="G107" s="61"/>
       <c r="J107" s="10"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.2">
@@ -3791,7 +3748,6 @@
         <v>0</v>
       </c>
       <c r="F108" s="13"/>
-      <c r="G108" s="61"/>
       <c r="J108" s="10"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.2">
@@ -3811,7 +3767,6 @@
         <v>0</v>
       </c>
       <c r="F109" s="13"/>
-      <c r="G109" s="61"/>
       <c r="J109" s="10"/>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.2">
@@ -3833,7 +3788,7 @@
       <c r="F110" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G110" s="65" t="s">
+      <c r="G110" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H110" s="16" t="s">
@@ -3865,7 +3820,7 @@
       <c r="F111" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G111" s="65" t="s">
+      <c r="G111" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H111" s="16" t="s">
@@ -3897,7 +3852,7 @@
       <c r="F112" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G112" s="65" t="s">
+      <c r="G112" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H112" s="16" t="s">
@@ -3927,7 +3882,6 @@
         <v>0</v>
       </c>
       <c r="F113" s="13"/>
-      <c r="G113" s="61"/>
       <c r="J113" s="10"/>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.2">
@@ -3947,7 +3901,6 @@
         <v>0</v>
       </c>
       <c r="F114" s="13"/>
-      <c r="G114" s="61"/>
       <c r="J114" s="10"/>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.2">
@@ -3967,7 +3920,6 @@
         <v>0</v>
       </c>
       <c r="F115" s="13"/>
-      <c r="G115" s="61"/>
       <c r="J115" s="10"/>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.2">
@@ -3987,7 +3939,6 @@
         <v>0</v>
       </c>
       <c r="F116" s="13"/>
-      <c r="G116" s="61"/>
       <c r="J116" s="10"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.2">
@@ -4007,7 +3958,6 @@
         <v>0</v>
       </c>
       <c r="F117" s="13"/>
-      <c r="G117" s="61"/>
       <c r="J117" s="10"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.2">
@@ -4027,7 +3977,6 @@
         <v>0</v>
       </c>
       <c r="F118" s="13"/>
-      <c r="G118" s="61"/>
       <c r="J118" s="10"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.2">
@@ -4049,7 +3998,7 @@
       <c r="F119" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G119" s="60" t="s">
+      <c r="G119" s="59" t="s">
         <v>41</v>
       </c>
       <c r="H119" s="16" t="s">
@@ -4081,7 +4030,7 @@
       <c r="F120" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G120" s="60" t="s">
+      <c r="G120" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H120" s="16" t="s">
@@ -4113,7 +4062,7 @@
       <c r="F121" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G121" s="60" t="s">
+      <c r="G121" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H121" s="16" t="s">
@@ -4143,7 +4092,6 @@
         <v>0</v>
       </c>
       <c r="F122" s="13"/>
-      <c r="G122" s="61"/>
       <c r="J122" s="10"/>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.2">
@@ -4163,7 +4111,6 @@
         <v>0</v>
       </c>
       <c r="F123" s="13"/>
-      <c r="G123" s="61"/>
       <c r="J123" s="10"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.2">
@@ -4183,7 +4130,6 @@
         <v>0</v>
       </c>
       <c r="F124" s="13"/>
-      <c r="G124" s="61"/>
       <c r="J124" s="10"/>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.2">
@@ -4203,7 +4149,6 @@
         <v>0</v>
       </c>
       <c r="F125" s="13"/>
-      <c r="G125" s="61"/>
       <c r="J125" s="10"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.2">
@@ -4223,7 +4168,6 @@
         <v>0</v>
       </c>
       <c r="F126" s="13"/>
-      <c r="G126" s="61"/>
       <c r="J126" s="10"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.2">
@@ -4243,7 +4187,6 @@
         <v>0</v>
       </c>
       <c r="F127" s="13"/>
-      <c r="G127" s="61"/>
       <c r="J127" s="10"/>
     </row>
     <row r="128" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -4265,7 +4208,7 @@
       <c r="F128" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G128" s="60" t="s">
+      <c r="G128" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H128" s="16" t="s">
@@ -4297,7 +4240,7 @@
       <c r="F129" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G129" s="60" t="s">
+      <c r="G129" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H129" s="16" t="s">
@@ -4329,7 +4272,7 @@
       <c r="F130" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G130" s="65" t="s">
+      <c r="G130" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H130" s="16" t="s">
@@ -4359,7 +4302,6 @@
         <v>0</v>
       </c>
       <c r="F131" s="13"/>
-      <c r="G131" s="61"/>
       <c r="J131" s="10"/>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.2">
@@ -4379,7 +4321,6 @@
         <v>0</v>
       </c>
       <c r="F132" s="13"/>
-      <c r="G132" s="61"/>
       <c r="J132" s="10"/>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.2">
@@ -4399,7 +4340,6 @@
         <v>0</v>
       </c>
       <c r="F133" s="13"/>
-      <c r="G133" s="61"/>
       <c r="J133" s="10"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.2">
@@ -4419,7 +4359,6 @@
         <v>0</v>
       </c>
       <c r="F134" s="13"/>
-      <c r="G134" s="61"/>
       <c r="J134" s="10"/>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.2">
@@ -4439,7 +4378,6 @@
         <v>0</v>
       </c>
       <c r="F135" s="13"/>
-      <c r="G135" s="61"/>
       <c r="J135" s="10"/>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.2">
@@ -4459,7 +4397,6 @@
         <v>0</v>
       </c>
       <c r="F136" s="13"/>
-      <c r="G136" s="61"/>
       <c r="J136" s="10"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.2">
@@ -4481,7 +4418,7 @@
       <c r="F137" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G137" s="60" t="s">
+      <c r="G137" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H137" s="16" t="s">
@@ -4513,7 +4450,7 @@
       <c r="F138" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G138" s="60" t="s">
+      <c r="G138" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H138" s="16" t="s">
@@ -4545,7 +4482,7 @@
       <c r="F139" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G139" s="60" t="s">
+      <c r="G139" s="59" t="s">
         <v>41</v>
       </c>
       <c r="H139" s="16" t="s">
@@ -4575,7 +4512,6 @@
         <v>0</v>
       </c>
       <c r="F140" s="13"/>
-      <c r="G140" s="61"/>
       <c r="J140" s="10"/>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.2">
@@ -4595,7 +4531,6 @@
         <v>0</v>
       </c>
       <c r="F141" s="13"/>
-      <c r="G141" s="61"/>
       <c r="J141" s="10"/>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.2">
@@ -4615,7 +4550,6 @@
         <v>0</v>
       </c>
       <c r="F142" s="13"/>
-      <c r="G142" s="61"/>
       <c r="J142" s="10"/>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.2">
@@ -4635,7 +4569,6 @@
         <v>0</v>
       </c>
       <c r="F143" s="13"/>
-      <c r="G143" s="61"/>
       <c r="J143" s="10"/>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.2">
@@ -4655,7 +4588,6 @@
         <v>0</v>
       </c>
       <c r="F144" s="13"/>
-      <c r="G144" s="61"/>
       <c r="J144" s="10"/>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.2">
@@ -4675,7 +4607,6 @@
         <v>0</v>
       </c>
       <c r="F145" s="13"/>
-      <c r="G145" s="61"/>
       <c r="J145" s="10"/>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.2">
@@ -4697,7 +4628,7 @@
       <c r="F146" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G146" s="65" t="s">
+      <c r="G146" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H146" s="16" t="s">
@@ -4729,7 +4660,7 @@
       <c r="F147" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G147" s="60" t="s">
+      <c r="G147" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H147" s="16" t="s">
@@ -4761,7 +4692,7 @@
       <c r="F148" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G148" s="60" t="s">
+      <c r="G148" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H148" s="16" t="s">
@@ -4791,7 +4722,6 @@
         <v>0</v>
       </c>
       <c r="F149" s="13"/>
-      <c r="G149" s="61"/>
       <c r="J149" s="10"/>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.2">
@@ -4811,7 +4741,6 @@
         <v>0</v>
       </c>
       <c r="F150" s="13"/>
-      <c r="G150" s="61"/>
       <c r="J150" s="10"/>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.2">
@@ -4831,7 +4760,6 @@
         <v>0</v>
       </c>
       <c r="F151" s="13"/>
-      <c r="G151" s="61"/>
       <c r="J151" s="10"/>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.2">
@@ -4851,7 +4779,6 @@
         <v>0</v>
       </c>
       <c r="F152" s="13"/>
-      <c r="G152" s="61"/>
       <c r="J152" s="10"/>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.2">
@@ -4871,7 +4798,6 @@
         <v>0</v>
       </c>
       <c r="F153" s="13"/>
-      <c r="G153" s="61"/>
       <c r="J153" s="10"/>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.2">
@@ -4891,7 +4817,6 @@
         <v>0</v>
       </c>
       <c r="F154" s="13"/>
-      <c r="G154" s="61"/>
       <c r="J154" s="10"/>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.2">
@@ -4913,7 +4838,7 @@
       <c r="F155" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G155" s="60" t="s">
+      <c r="G155" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H155" s="16" t="s">
@@ -4945,7 +4870,7 @@
       <c r="F156" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G156" s="60" t="s">
+      <c r="G156" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H156" s="16" t="s">
@@ -4977,7 +4902,7 @@
       <c r="F157" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G157" s="60" t="s">
+      <c r="G157" s="59" t="s">
         <v>41</v>
       </c>
       <c r="H157" s="16" t="s">
@@ -5007,7 +4932,6 @@
         <v>0</v>
       </c>
       <c r="F158" s="13"/>
-      <c r="G158" s="61"/>
       <c r="J158" s="10"/>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.2">
@@ -5027,7 +4951,6 @@
         <v>0</v>
       </c>
       <c r="F159" s="13"/>
-      <c r="G159" s="61"/>
       <c r="J159" s="10"/>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.2">
@@ -5047,7 +4970,6 @@
         <v>0</v>
       </c>
       <c r="F160" s="13"/>
-      <c r="G160" s="61"/>
       <c r="J160" s="10"/>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.2">
@@ -5067,7 +4989,6 @@
         <v>0</v>
       </c>
       <c r="F161" s="13"/>
-      <c r="G161" s="61"/>
       <c r="J161" s="10"/>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.2">
@@ -5087,7 +5008,6 @@
         <v>0</v>
       </c>
       <c r="F162" s="13"/>
-      <c r="G162" s="61"/>
       <c r="J162" s="10"/>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.2">
@@ -5107,7 +5027,6 @@
         <v>0</v>
       </c>
       <c r="F163" s="13"/>
-      <c r="G163" s="61"/>
       <c r="J163" s="10"/>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.2">
@@ -5129,7 +5048,7 @@
       <c r="F164" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G164" s="60" t="s">
+      <c r="G164" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H164" s="44" t="s">
@@ -5161,7 +5080,7 @@
       <c r="F165" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G165" s="60" t="s">
+      <c r="G165" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H165" s="44" t="s">
@@ -5191,7 +5110,6 @@
         <v>0</v>
       </c>
       <c r="F166" s="13"/>
-      <c r="G166" s="61"/>
       <c r="J166" s="10"/>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.2">
@@ -5211,7 +5129,6 @@
         <v>0</v>
       </c>
       <c r="F167" s="13"/>
-      <c r="G167" s="61"/>
       <c r="J167" s="10"/>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.2">
@@ -5231,7 +5148,6 @@
         <v>0</v>
       </c>
       <c r="F168" s="13"/>
-      <c r="G168" s="61"/>
       <c r="J168" s="10"/>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.2">
@@ -5251,7 +5167,6 @@
         <v>0</v>
       </c>
       <c r="F169" s="13"/>
-      <c r="G169" s="61"/>
       <c r="J169" s="10"/>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.2">
@@ -5271,7 +5186,6 @@
         <v>0</v>
       </c>
       <c r="F170" s="13"/>
-      <c r="G170" s="61"/>
       <c r="J170" s="10"/>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.2">
@@ -5291,7 +5205,6 @@
         <v>0</v>
       </c>
       <c r="F171" s="13"/>
-      <c r="G171" s="61"/>
       <c r="J171" s="10"/>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.2">
@@ -5311,7 +5224,6 @@
         <v>0</v>
       </c>
       <c r="F172" s="13"/>
-      <c r="G172" s="61"/>
       <c r="J172" s="10"/>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.2">
@@ -5333,7 +5245,7 @@
       <c r="F173" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G173" s="60" t="s">
+      <c r="G173" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H173" s="44" t="s">
@@ -5365,7 +5277,7 @@
       <c r="F174" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G174" s="60" t="s">
+      <c r="G174" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H174" s="44" t="s">
@@ -5395,7 +5307,6 @@
         <v>0</v>
       </c>
       <c r="F175" s="13"/>
-      <c r="G175" s="61"/>
       <c r="J175" s="10"/>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.2">
@@ -5415,7 +5326,6 @@
         <v>0</v>
       </c>
       <c r="F176" s="13"/>
-      <c r="G176" s="61"/>
       <c r="J176" s="10"/>
     </row>
     <row r="177" spans="1:10" x14ac:dyDescent="0.2">
@@ -5435,7 +5345,6 @@
         <v>0</v>
       </c>
       <c r="F177" s="13"/>
-      <c r="G177" s="61"/>
       <c r="J177" s="10"/>
     </row>
     <row r="178" spans="1:10" x14ac:dyDescent="0.2">
@@ -5455,7 +5364,6 @@
         <v>0</v>
       </c>
       <c r="F178" s="13"/>
-      <c r="G178" s="61"/>
       <c r="J178" s="10"/>
     </row>
     <row r="179" spans="1:10" x14ac:dyDescent="0.2">
@@ -5475,7 +5383,6 @@
         <v>0</v>
       </c>
       <c r="F179" s="13"/>
-      <c r="G179" s="61"/>
       <c r="J179" s="10"/>
     </row>
     <row r="180" spans="1:10" x14ac:dyDescent="0.2">
@@ -5495,7 +5402,6 @@
         <v>0</v>
       </c>
       <c r="F180" s="13"/>
-      <c r="G180" s="61"/>
       <c r="J180" s="10"/>
     </row>
     <row r="181" spans="1:10" x14ac:dyDescent="0.2">
@@ -5515,7 +5421,6 @@
         <v>0</v>
       </c>
       <c r="F181" s="13"/>
-      <c r="G181" s="61"/>
       <c r="J181" s="10"/>
     </row>
     <row r="182" spans="1:10" x14ac:dyDescent="0.2">
@@ -5537,7 +5442,7 @@
       <c r="F182" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G182" s="60" t="s">
+      <c r="G182" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H182" s="44" t="s">
@@ -5569,7 +5474,7 @@
       <c r="F183" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G183" s="60" t="s">
+      <c r="G183" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H183" s="44" t="s">
@@ -5599,7 +5504,6 @@
         <v>0</v>
       </c>
       <c r="F184" s="13"/>
-      <c r="G184" s="61"/>
       <c r="J184" s="10"/>
     </row>
     <row r="185" spans="1:10" x14ac:dyDescent="0.2">
@@ -5619,7 +5523,6 @@
         <v>0</v>
       </c>
       <c r="F185" s="13"/>
-      <c r="G185" s="61"/>
       <c r="J185" s="10"/>
     </row>
     <row r="186" spans="1:10" x14ac:dyDescent="0.2">
@@ -5639,7 +5542,6 @@
         <v>0</v>
       </c>
       <c r="F186" s="13"/>
-      <c r="G186" s="61"/>
       <c r="J186" s="10"/>
     </row>
     <row r="187" spans="1:10" x14ac:dyDescent="0.2">
@@ -5659,7 +5561,6 @@
         <v>0</v>
       </c>
       <c r="F187" s="13"/>
-      <c r="G187" s="61"/>
       <c r="J187" s="10"/>
     </row>
     <row r="188" spans="1:10" x14ac:dyDescent="0.2">
@@ -5679,7 +5580,6 @@
         <v>0</v>
       </c>
       <c r="F188" s="13"/>
-      <c r="G188" s="61"/>
       <c r="J188" s="10"/>
     </row>
     <row r="189" spans="1:10" x14ac:dyDescent="0.2">
@@ -5699,7 +5599,6 @@
         <v>0</v>
       </c>
       <c r="F189" s="13"/>
-      <c r="G189" s="61"/>
       <c r="J189" s="10"/>
     </row>
     <row r="190" spans="1:10" x14ac:dyDescent="0.2">
@@ -5719,7 +5618,6 @@
         <v>0</v>
       </c>
       <c r="F190" s="13"/>
-      <c r="G190" s="61"/>
       <c r="J190" s="10"/>
     </row>
     <row r="191" spans="1:10" x14ac:dyDescent="0.2">
@@ -5741,7 +5639,7 @@
       <c r="F191" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G191" s="60" t="s">
+      <c r="G191" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H191" s="44" t="s">
@@ -5773,7 +5671,7 @@
       <c r="F192" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G192" s="60" t="s">
+      <c r="G192" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H192" s="44" t="s">
@@ -5803,7 +5701,6 @@
         <v>0</v>
       </c>
       <c r="F193" s="13"/>
-      <c r="G193" s="61"/>
       <c r="J193" s="10"/>
     </row>
     <row r="194" spans="1:13" x14ac:dyDescent="0.2">
@@ -5823,7 +5720,6 @@
         <v>0</v>
       </c>
       <c r="F194" s="13"/>
-      <c r="G194" s="61"/>
       <c r="J194" s="10"/>
     </row>
     <row r="195" spans="1:13" x14ac:dyDescent="0.2">
@@ -5843,7 +5739,6 @@
         <v>0</v>
       </c>
       <c r="F195" s="13"/>
-      <c r="G195" s="61"/>
       <c r="J195" s="10"/>
     </row>
     <row r="196" spans="1:13" x14ac:dyDescent="0.2">
@@ -5863,7 +5758,6 @@
         <v>0</v>
       </c>
       <c r="F196" s="13"/>
-      <c r="G196" s="61"/>
       <c r="J196" s="10"/>
     </row>
     <row r="197" spans="1:13" x14ac:dyDescent="0.2">
@@ -5883,7 +5777,6 @@
         <v>0</v>
       </c>
       <c r="F197" s="13"/>
-      <c r="G197" s="61"/>
       <c r="J197" s="10"/>
     </row>
     <row r="198" spans="1:13" x14ac:dyDescent="0.2">
@@ -5903,7 +5796,6 @@
         <v>0</v>
       </c>
       <c r="F198" s="13"/>
-      <c r="G198" s="61"/>
       <c r="J198" s="10"/>
     </row>
     <row r="199" spans="1:13" x14ac:dyDescent="0.2">
@@ -5923,7 +5815,6 @@
         <v>0</v>
       </c>
       <c r="F199" s="13"/>
-      <c r="G199" s="61"/>
       <c r="J199" s="10"/>
     </row>
     <row r="200" spans="1:13" x14ac:dyDescent="0.2">
@@ -5945,7 +5836,7 @@
       <c r="F200" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G200" s="60" t="s">
+      <c r="G200" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H200" s="44" t="s">
@@ -5977,7 +5868,7 @@
       <c r="F201" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="G201" s="60" t="s">
+      <c r="G201" s="59" t="s">
         <v>43</v>
       </c>
       <c r="H201" s="44" t="s">
@@ -6007,7 +5898,6 @@
         <v>0</v>
       </c>
       <c r="F202" s="13"/>
-      <c r="G202" s="61"/>
       <c r="J202" s="10"/>
     </row>
     <row r="203" spans="1:13" x14ac:dyDescent="0.2">
@@ -6027,7 +5917,6 @@
         <v>0</v>
       </c>
       <c r="F203" s="13"/>
-      <c r="G203" s="61"/>
       <c r="J203" s="10"/>
     </row>
     <row r="204" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6047,7 +5936,6 @@
         <v>0</v>
       </c>
       <c r="F204" s="13"/>
-      <c r="G204" s="61"/>
       <c r="J204" s="10"/>
     </row>
     <row r="205" spans="1:13" x14ac:dyDescent="0.2">
@@ -6067,7 +5955,6 @@
         <v>0</v>
       </c>
       <c r="F205" s="13"/>
-      <c r="G205" s="61"/>
       <c r="J205" s="10"/>
       <c r="L205" s="20" t="s">
         <v>15</v>
@@ -6094,7 +5981,6 @@
         <v>0</v>
       </c>
       <c r="F206" s="13"/>
-      <c r="G206" s="61"/>
       <c r="J206" s="10"/>
       <c r="L206" s="9" t="s">
         <v>16</v>
@@ -6121,7 +6007,6 @@
         <v>0</v>
       </c>
       <c r="F207" s="13"/>
-      <c r="G207" s="61"/>
       <c r="J207" s="10"/>
       <c r="L207" s="9" t="s">
         <v>17</v>
@@ -6148,7 +6033,6 @@
         <v>0</v>
       </c>
       <c r="F208" s="13"/>
-      <c r="G208" s="61"/>
       <c r="J208" s="10"/>
       <c r="L208" s="11" t="s">
         <v>18</v>
@@ -6177,7 +6061,7 @@
       <c r="F209" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="G209" s="60" t="s">
+      <c r="G209" s="59" t="s">
         <v>41</v>
       </c>
       <c r="H209" s="44" t="s">
@@ -6213,7 +6097,7 @@
       <c r="F210" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G210" s="65" t="s">
+      <c r="G210" s="61" t="s">
         <v>42</v>
       </c>
       <c r="H210" s="44" t="s">
@@ -6243,7 +6127,6 @@
         <v>0</v>
       </c>
       <c r="F211" s="13"/>
-      <c r="G211" s="61"/>
       <c r="J211" s="10"/>
     </row>
     <row r="212" spans="1:13" x14ac:dyDescent="0.2">
@@ -6263,7 +6146,6 @@
         <v>0</v>
       </c>
       <c r="F212" s="13"/>
-      <c r="G212" s="61"/>
       <c r="J212" s="10"/>
     </row>
     <row r="213" spans="1:13" x14ac:dyDescent="0.2">
@@ -6283,7 +6165,6 @@
         <v>0</v>
       </c>
       <c r="F213" s="13"/>
-      <c r="G213" s="61"/>
       <c r="J213" s="10"/>
     </row>
     <row r="214" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
@@ -6303,7 +6184,6 @@
         <v>0</v>
       </c>
       <c r="F214" s="13"/>
-      <c r="G214" s="61"/>
       <c r="H214" s="15"/>
       <c r="I214" s="15"/>
       <c r="J214" s="12"/>
@@ -6332,7 +6212,7 @@
         <f>SUM(B215:E215)</f>
         <v>66</v>
       </c>
-      <c r="G215" s="62"/>
+      <c r="G215" s="20"/>
       <c r="H215" s="38"/>
       <c r="I215" s="57" t="s">
         <v>32</v>
